--- a/stories/arbres/ATOM-LAN.SON.001-10.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaston est près de la fenêtre. Maman ouvre un peu. Un son : plic plic. Maman dit : c'est un son. Quel nom ? Gaston dit : la pluie. Un son : miaou. Gaston dit le nom : le chat. Papa arrive. Un son : tchou tchou. Papa dit : c'est un son. Quel nom ? Gaston dit : le train. Maman dit : on entend un son. On dit le nom. Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.</t>
+          <t>Gaston est près de la fenêtre. Maman ouvre un peu. Un son : plic plic. C'est un son. Quel nom ? La pluie. Un son : miaou. Gaston dit le nom : le chat. Papa arrive. Un son : tchou tchou. C'est un son. Quel nom ? Le train. On entend un son. On dit le nom. Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston est près de la fenêtre. Maman ouvre un peu. Un son : plic plic.
+maman|C'est un son. Quel nom ?
+enfant-m|La pluie.
+narrateur|Un son : miaou. Gaston dit le nom : le chat. Papa arrive. Un son : tchou tchou.
+papa|C'est un son. Quel nom ?
+enfant-m|Le train.
+maman|On entend un son. On dit le nom.
+narrateur|Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston a entendu un son. Il a dit le nom. Pluie. Chat. Train.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa ferme un peu la fenêtre. Gaston écoute encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-10.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Gaston entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Gaston a entendu un son. Il a dit le nom. Pluie. Chat. Train.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Papa ferme un peu la fenêtre. Gaston écoute encore.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-10.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaston nomme les sons de la fenêtre</t>
+          <t>La vitre d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un chausson jaune attend. Aniss nomme la pluie, le chat, le train. Papa ferme un peu la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaston est près de la fenêtre. Maman ouvre un peu. Un son : plic plic. C'est un son. Quel nom ? La pluie. Un son : miaou. Gaston dit le nom : le chat. Papa arrive. Un son : tchou tchou. C'est un son. Quel nom ? Le train. On entend un son. On dit le nom. Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.</t>
+          <t>Un chausson jaune attend. Il est près du radiateur. Le radiateur est chaud. La vitre a des petits chemins. Ce sont des chemins d'eau. La maison sent la soupe. Aniss, viens. En ce moment, Aniss s'assoit. Le tapis est doux. Maman ouvre un peu. Un son arrive. Plic plic. C'est un son. Quel nom ? La pluie. Oui. Le nom, c'est la pluie. Une goutte glisse. Elle descend. Oui. Un son. Miaou. Quel nom ? Le chat. Oui. Le chat vient. Son poil est chaud. Papa arrive. Un son long. Tchou tchou. C'est un son. Quel nom ? Le train. Oui. On entend un son. On dit le nom. Son. Nom. Aniss répète. Pluie. Chat. Train. Bravo, Aniss. Tu as dit le nom. La soupe sent encore. Aniss pose la main sur la vitre. Elle est froide. Oui. La vitre est froide. Le son a un nom. La pluie. Oui. Une goutte glisse encore. Le chat ronronne. C'est un son. Quel nom ? Le chat. Oui. Tu as fini d'écouter ? Encore un peu. D'accord. Le chausson jaune attend toujours.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gaston est près de la fenêtre. Maman ouvre un peu. Un son : plic plic.
-maman|C'est un son. Quel nom ?
+          <t>narrateur|Un chausson jaune attend.
+narrateur|Il est près du radiateur.
+narrateur|Le radiateur est chaud.
+narrateur|La vitre a des petits chemins.
+narrateur|Ce sont des chemins d'eau.
+narrateur|La maison sent la soupe.
+maman|Aniss, viens.
+narrateur|En ce moment, Aniss s'assoit.
+narrateur|Le tapis est doux.
+narrateur|Maman ouvre un peu.
+narrateur|Un son arrive.
+narrateur|Plic plic.
+maman|C'est un son.
+maman|Quel nom ?
 enfant-m|La pluie.
-narrateur|Un son : miaou. Gaston dit le nom : le chat. Papa arrive. Un son : tchou tchou.
-papa|C'est un son. Quel nom ?
+maman|Oui.
+maman|Le nom, c'est la pluie.
+narrateur|Une goutte glisse.
+enfant-m|Elle descend.
+maman|Oui.
+narrateur|Un son.
+narrateur|Miaou.
+maman|Quel nom ?
+enfant-m|Le chat.
+maman|Oui.
+narrateur|Le chat vient.
+narrateur|Son poil est chaud.
+narrateur|Papa arrive.
+narrateur|Un son long.
+narrateur|Tchou tchou.
+papa|C'est un son.
+papa|Quel nom ?
 enfant-m|Le train.
-maman|On entend un son. On dit le nom.
-narrateur|Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.</t>
+papa|Oui.
+maman|On entend un son.
+maman|On dit le nom.
+enfant-m|Son.
+enfant-m|Nom.
+narrateur|Aniss répète.
+enfant-m|Pluie.
+enfant-m|Chat.
+enfant-m|Train.
+papa|Bravo, Aniss.
+maman|Tu as dit le nom.
+narrateur|La soupe sent encore.
+narrateur|Aniss pose la main sur la vitre.
+enfant-m|Elle est froide.
+maman|Oui.
+maman|La vitre est froide.
+papa|Le son a un nom.
+enfant-m|La pluie.
+papa|Oui.
+narrateur|Une goutte glisse encore.
+narrateur|Le chat ronronne.
+maman|C'est un son.
+maman|Quel nom ?
+enfant-m|Le chat.
+maman|Oui.
+papa|Tu as fini d'écouter ?
+enfant-m|Encore un peu.
+maman|D'accord.
+narrateur|Le chausson jaune attend toujours.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gaston entend un bruit. C'est quoi ?</t>
+          <t>Aniss entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gaston entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Aniss entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gaston a entendu un son. Il a dit le nom. Pluie. Chat. Train.</t>
+          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Chat. Train. Tu as nommé le son ? Oui. Bravo. Tu as fait du bon travail. Le chat se frotte. Aniss pose la main. Il est doux. Oui. On entend un son. On dit le nom. Le chat. Oui. La vitre a encore des chemins. Ils descendent. Oui. On a entendu des sons. On a dit les noms. Pluie, chat, train. Bravo. Le radiateur reste chaud. Aniss pose le pied près du chausson.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1742,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gaston a entendu un son. Il a dit le nom. Pluie. Chat. Train.</t>
+          <t>narrateur|Aniss a entendu un son.
+narrateur|Il a dit le nom.
+narrateur|Pluie.
+narrateur|Chat.
+narrateur|Train.
+maman|Tu as nommé le son ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le chat se frotte.
+narrateur|Aniss pose la main.
+enfant-m|Il est doux.
+maman|Oui.
+maman|On entend un son.
+maman|On dit le nom.
+enfant-m|Le chat.
+papa|Oui.
+narrateur|La vitre a encore des chemins.
+enfant-m|Ils descendent.
+maman|Oui.
+papa|On a entendu des sons.
+maman|On a dit les noms.
+enfant-m|Pluie, chat, train.
+papa|Bravo.
+narrateur|Le radiateur reste chaud.
+narrateur|Aniss pose le pied près du chausson.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1795,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa ferme un peu la fenêtre. Gaston écoute encore.</t>
+          <t>On ferme un peu ? Oui. Papa ferme un peu la fenêtre. Aniss écoute encore. Le chausson jaune attend. Tu as fini d'écouter ? Oui, maman. Merci. Bravo. La soupe mijote tout bas. Le chat s'endort. Tu as nommé le son. Oui. Bravo, Aniss. Le tapis est encore doux. La maison sent la soupe.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1931,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa ferme un peu la fenêtre. Gaston écoute encore.</t>
+          <t>papa|On ferme un peu ?
+enfant-m|Oui.
+narrateur|Papa ferme un peu la fenêtre.
+narrateur|Aniss écoute encore.
+narrateur|Le chausson jaune attend.
+maman|Tu as fini d'écouter ?
+enfant-m|Oui, maman.
+papa|Merci.
+maman|Bravo.
+narrateur|La soupe mijote tout bas.
+narrateur|Le chat s'endort.
+papa|Tu as nommé le son.
+enfant-m|Oui.
+maman|Bravo, Aniss.
+narrateur|Le tapis est encore doux.
+narrateur|La maison sent la soupe.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Pluie, chat, train. Bravo, Aniss. La vitre redevient calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2114,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit le nom.
+papa|Oui.
+maman|Pluie, chat, train.
+papa|Bravo, Aniss.
+narrateur|La vitre redevient calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2179,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-10.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-10.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaston est près de la fenêtre. Maman ouvre un peu. Un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt; : plic plic. Maman dit : c'est un son. Quel nom ? Gaston dit : la pluie. Un son : miaou. Gaston dit le nom : le chat. Papa arrive. Un son : tchou tchou. Papa dit : c'est un son. Quel nom ? Gaston dit : le train. Maman dit : on entend un son. On dit le nom. Gaston répète. Pluie. Chat. Train. C'est un son. On dit le nom.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un chausson jaune attend. Il est près du radiateur. Le radiateur est chaud. La vitre a des petits chemins. Ce sont des chemins d'eau. La maison sent la soupe. Aniss, viens. En ce moment, Aniss s'assoit. Le tapis est doux. Maman ouvre un peu. Un son arrive. Plic plic. C'est un son. Quel nom ? La pluie. Oui. Le nom, c'est la pluie. Une goutte glisse. Elle descend. Oui. Un son. Miaou. Quel nom ? Le chat. Oui. Le chat vient. Son poil est chaud. Papa arrive. Un son long. Tchou tchou. C'est un son. Quel nom ? Le train. Oui. On entend un son. On dit le nom. Son. Nom. Aniss répète. Pluie. Chat. Train. Bravo, Aniss. Tu as dit le nom. La soupe sent encore. Aniss pose la main sur la vitre. Elle est froide. Oui. La vitre est froide. Le son a un nom. La pluie. Oui. Une goutte glisse encore. Le chat ronronne. C'est un son. Quel nom ? Le chat. Oui. Tu as fini d'écouter ? Encore un peu. D'accord. Le chausson jaune attend toujours.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1388,7 +1388,6 @@
 narrateur|Le chausson jaune attend toujours.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaston entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1573,7 +1572,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Chat. Train. Tu as nommé le son ? Oui. Bravo. Tu as fait du bon travail. Le chat se frotte. Aniss pose la main. Il est doux. Oui. On entend un son. On dit le nom. Le chat. Oui. La vitre a encore des chemins. Ils descendent. Oui. On a entendu des sons. On a dit les noms. Pluie, chat, train. Bravo. Le radiateur reste chaud. Aniss pose le pied près du chausson.</t>
+          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Chat. Train. Tu as nommé le son ? Oui. Bravo. Le chat se frotte. Aniss pose la main. Il est doux. Oui. On entend un son. On dit le nom. Le chat. Oui. La vitre a encore des chemins. Ils descendent. Oui. On a entendu des sons. On a dit les noms. Pluie, chat, train. Bravo. Le radiateur reste chaud. Aniss pose le pied près du chausson.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaston a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Il a dit le nom. Pluie. Chat. Train.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Chat. Train. Tu as nommé le son ? Oui. Bravo. Le chat se frotte. Aniss pose la main. Il est doux. Oui. On entend un son. On dit le nom. Le chat. Oui. La vitre a encore des chemins. Ils descendent. Oui. On a entendu des sons. On a dit les noms. Pluie, chat, train. Bravo. Le radiateur reste chaud. Aniss pose le pied près du chausson.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1748,6 @@
 maman|Tu as nommé le son ?
 enfant-m|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le chat se frotte.
 narrateur|Aniss pose la main.
 enfant-m|Il est doux.
@@ -1770,7 +1767,6 @@
 narrateur|Aniss pose le pied près du chausson.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1800,7 +1796,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa ferme un peu la fenêtre. Gaston écoute encore.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On ferme un peu ? Oui. Papa ferme un peu la fenêtre. Aniss écoute encore. Le chausson jaune attend. Tu as fini d'écouter ? Oui, maman. Merci. Bravo. La soupe mijote tout bas. Le chat s'endort. Tu as nommé le son. Oui. Bravo, Aniss. Le tapis est encore doux. La maison sent la soupe.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,7 +1945,6 @@
 narrateur|La maison sent la soupe.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1974,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le nom. Oui. Pluie, chat, train. Bravo, Aniss. La vitre redevient calme. L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Pluie, chat, train. Bravo, Aniss. La vitre redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le nom. Oui. Pluie, chat, train. Bravo, Aniss. La vitre redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2118,11 +2113,9 @@
 papa|Oui.
 maman|Pluie, chat, train.
 papa|Bravo, Aniss.
-narrateur|La vitre redevient calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La vitre redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2141,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-10.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-10.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gaston, maman, papa</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
